--- a/UTCUTS/A1_Outputs/A-O_AR_Projections_COMPLETED.xlsx
+++ b/UTCUTS/A1_Outputs/A-O_AR_Projections_COMPLETED.xlsx
@@ -26699,7 +26699,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED88F7EC-70BB-4ECF-8542-8235E9318E7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AB457CE-7F43-48CD-933A-C22185F47522}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
